--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>140 ea</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Backfield 48" autocannons + cheap OC6 body / screen.</t>
+          <t>TWO backfield 48" autocannon platforms + OC6 screens — the points-efficient fill (a single Armiger wastes ~95 pts) + extra OC for the melee-heavy meta.</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>As written ~1825-1915 / 2000 with NO enhancements = the one concrete error. Add the 3 enhancements above to reach 2000 (Rotate is free). VERIFY exact points vs LIVE MFM before submitting — BSData prices Castellan 400, the app may be 425.</t>
+          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
         </is>
       </c>
     </row>
@@ -1405,51 +1405,51 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Lancer's Sigil</t>
+          <t>Blessed Plate  [TAKEN]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cerastus Knight Lancer</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>(25) Re-roll the Lancer's charge — with only ONE decapitation blade, guaranteeing its decisive charge is the highest-value 25 pts in the list.</t>
+          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Blessed Plate</t>
+          <t>Bearer of the Judicant's Helm  [bench]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Knight Castellan #1</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>(30) Castellan -&gt; T13: the Volcano platform survives the incoming longer.</t>
+          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm</t>
+          <t>Sanctuary  [bench]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Knight Castellan #2</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain; beats intervening-terrain cover.</t>
+          <t>(20) 5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>As written ~1825-1915 / 2000 with NO enhancements = the one concrete error. Add the 3 enhancements above to reach 2000 (Rotate is free). VERIFY exact points vs LIVE MFM before submitting — BSData prices Castellan 400, the app may be 425.</t>
+          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
         </is>
       </c>
     </row>
@@ -1665,51 +1665,51 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Lancer's Sigil</t>
+          <t>Blessed Plate  [TAKEN]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cerastus Knight Lancer</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>(25) Re-roll the Lancer's charge — with only ONE decapitation blade, guaranteeing its decisive charge is the highest-value 25 pts in the list.</t>
+          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Blessed Plate</t>
+          <t>Bearer of the Judicant's Helm  [bench]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Knight Castellan #1</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>(30) Castellan -&gt; T13: the Volcano platform survives the incoming longer.</t>
+          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm</t>
+          <t>Sanctuary  [bench]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Knight Castellan #2</t>
+          <t>a Knight Castellan</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain; beats intervening-terrain cover.</t>
+          <t>(20) 5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>List A removes ~1-2 more things per turn AT RANGE (dominates the shooting phase); List B survives + counter-punches one more MELEE lane (wins the fight phase you can't tank). Which matters more = which half of the meta you expect to face, and which losses hurt most. Points are near-identical (~1825-1840 base each; verify Castellan 400 vs app-425 against LIVE MFM before submitting).</t>
+          <t>List A removes ~1-2 more things per turn AT RANGE (dominates the shooting phase); List B survives + counter-punches one more MELEE lane (wins the fight phase you can't tank). Which matters more = which half of the meta you expect to face, and which losses hurt most. Points are near-identical (~1825-1840 base each; Castellan escalates 425/450, Crusader 410 w/RFBC — confirm Lancer/Armiger vs MFM).</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Custodes (4), Blood Angels (4), DA Deathwing (~3), Thousand Sons (3), Chaos Daemons Khorne (~2), Iron Hands Terminators (~2), Orks (9, but a loss either way)</t>
+          <t>Custodes (4), Blood Angels (4), DA Deathwing (~3), Thousand Sons (3), Chaos Daemons Khorne (~2), Iron Hands Terminators (~2), Orks (8, but a loss either way)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <row r="18" ht="340" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IT'S CLOSE — and that's the honest headline. Prevalence-weighted, the field splits almost evenly: ~25 of 75 lean LIST A (the ranged-anti-tank half), ~18 lean LIST B plus the 9 un-winnable Orks, and ~19 are EVEN (led by the #1-tie Emperor's Children). The meta is ~57% melee-forward BY BODY, which argues for the 2nd Lancer — BUT the matchups that leans decide are asymmetric.
+          <t>IT'S CLOSE — and that's the honest headline. Prevalence-weighted, the field splits almost evenly: ~24 of 70 lean LIST A (the ranged-anti-tank half), ~17 lean LIST B plus the 8 un-winnable Orks, and ~19 are EVEN (led by the #1-tie Emperor's Children). The meta is ~57% melee-forward BY BODY, which argues for the 2nd Lancer — BUT the matchups that leans decide are asymmetric.
 RECOMMENDATION: LIST A (2 Castellan / 1 Lancer), narrowly, for three data-grounded reasons:
 1) WORST-CASE MITIGATION. The A-favoured matchups (T'au, AdMech, Astra Militarum, Votann = ~16 prevalence of pure ranged anti-tank) are the ones that TABLE a Knight army 0-VP. You LOSE games there. List B surrenders those ranged duels (one Volcano, not two) for a fight-phase edge in matchups you can often still finesse on the MISSION.
 2) THE MELEE MAJORITY IS BEATABLE WITHOUT THE 2ND BLADE. The biggest melee chunks are hordes/chaff (EC Daemonettes, Ork Boyz) that SHOOTING thins as well as a Lancer would, and the ELITE melee (Custodes/BA/DA) you beat by OUT-OC-ing on the primary + screening the alpha (Navigator dome) + 1 Lancer counter-charging the key lane — not by trying to win the fight phase outright.
@@ -741,7 +741,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>n=75 top-finishing lists (every entry went X-1 or better; incl. the 8-0 Tacoma winner and 7-0 Edinburgh Major). This is a WINNERS' meta (what beats the field), post-Dataslate, late July 2026 — the exact filth LSO's top tables will bring. Counts are of top lists, not raw popularity, so read them as 'what's winning', prevalence-weighted.</t>
+          <t>n=70 top-finishing lists dated ON/AFTER 2026-07-23 (post-Dataslate cutoff: the 7/22 Dataslate reset points/rules, so pre-7/23 GTs incl. Tacoma 7/17 + Edinburgh 7/18 are EXCLUDED). WINNERS' meta, late July 2026 — the exact filth LSO's top tables will bring. Counts are of top lists, not raw popularity, so read them as 'what's winning', prevalence-weighted.</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>#1-tie AND the 8-0 Tacoma winner. ~100 Boyz + klaws out-OC/tarpit; loss either way — 2nd Lancer sweep+4++ survives it marginally better.</t>
+          <t>#2 (behind EC). ~100 Boyz + klaws out-OC/tarpit; loss either way — 2nd Lancer sweep+4++ survives it marginally better.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
@@ -1100,11 +1100,11 @@
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Tyranids (Crusher Stampede / Invasion Fleet)</t>
+          <t>Tyranids (Crusher Stampede)</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
@@ -1175,11 +1175,11 @@
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Long tail (Aeldari Windrider, Death Guard, Adepta Sororitas, Chaos Knights)</t>
+          <t>Long tail (Aeldari Windrider, Death Guard, Chaos Knights)</t>
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>400 ea</t>
+          <t>425 + 450</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>The shooting core. 2x Volcano (D3 shots ea, ~23 dmg) one-shots no-invuln anchors + snipes characters; plasma decimator anti-elite volume; +1 hit vs terrain (Dominus).</t>
+          <t>The shooting core (escalating: 1st 425, 2nd 450). 2x Volcano (D3 shots ea, ~23 dmg) one-shots no-invuln anchors + snipes; plasma decimator anti-elite; +1 hit vs terrain (Dominus). #1 bears Archeotech Autoloaders (re-roll the shot count on the D3/D6+3 guns).</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Rapid-fire battle cannon (D6+3 S10), Avenger gatling (A18 S6 AP-2 D2), heavy flamer, thermal cannon (2D3 S12 AP-4 Melta6), stubber, feet</t>
+          <t>Rapid-fire battle cannon (D6+3 S10, +15pts), Avenger gatling (A18 S6 AP-2 D2), heavy flamer, thermal cannon (2D3 S12 AP-4 Melta6), stubber, feet</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>410</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>Anti-infantry SUBTRACTION: RFBC + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
+          <t>395 base + 15 for the RFBC. Anti-infantry SUBTRACTION: RFBC + Avenger A18 strip soft OC; thermal for anti-tank/Speeders.</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>140 ea</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>TWO backfield 48" autocannon platforms + OC6 screens — the points-efficient fill (a single Armiger wastes ~95 pts) + extra OC for the melee-heavy meta.</t>
+          <t>Backfield 48" autocannon platform + OC6 screen.</t>
         </is>
       </c>
     </row>
@@ -1379,19 +1379,19 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>~75</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>12" anti-Deep-Strike dome (vs BA/SW/GSC/deep-strike alphas) + Hidden home-holder. Allies take no enhancement.</t>
+          <t>12" anti-Deep-Strike dome (vs BA/SW/GSC/deep-strike alphas) + Hidden home-holder. Allies take no enhancement. (75 confirmed from Scott Ketcham's Tacoma roster.)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
+          <t>1,970 / 2000 (30 spare) — MFM points: Castellan 425 + 450 (escalating) + Crusader 410 (395 +15 RFBC) + Cerastus Lancer 415 + Armiger Helverin 140 + Navigator 75 = 1,915, + Archeotech Autoloaders 25 + Blessed Plate 30 = 1,970. ONE Armiger (the correct build — the earlier '2 Armiger' was an error from stale BSData points). NO Lancer's Sigil. All points MFM-verified (1,970/2000 from data/mfm/imperial-knights.json).</t>
         </is>
       </c>
     </row>
@@ -1405,57 +1405,39 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Blessed Plate  [TAKEN]</t>
+          <t>Archeotech Autoloaders  [TAKEN — Castellan #1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
+          <t>(25) Re-roll the number of Attacks (shots) of a weapon — huge on the Volcano lance (D3 shots) and plasma decimator (D6+3), turning low shot-rolls into full salvoes. The shooting-dominant enhancement.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm  [bench]</t>
+          <t>Blessed Plate  [TAKEN — Castellan #2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Sanctuary  [bench]</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>a Knight Castellan</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>(20) 5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
+          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the second Volcano platform.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C14:E14"/>
+  <mergeCells count="5">
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
@@ -1472,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1651,7 +1633,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED 1,995 / 2000: 2x Castellan 400 + Cerastus Lancer 415 + Crusader 395 + 2x Armiger Helverin 140 + Navigator 75 = 1,965, + Blessed Plate 30 = 1,995 (5 spare). Points from BSData = current MFM (Castellan 400 confirmed, not 425). NO Lancer's Sigil (rejected). The 2nd Armiger is the points-efficient fill — a single Armiger wastes ~95 pts the enhancement allowance can't absorb.</t>
+          <t>1,970 / 2000 (30 spare) — MFM points: Castellan 425 + 450 (escalating) + Crusader 410 (395 +15 RFBC) + Cerastus Lancer 415 + Armiger Helverin 140 + Navigator 75 = 1,915, + Archeotech Autoloaders 25 + Blessed Plate 30 = 1,970. ONE Armiger (the correct build — the earlier '2 Armiger' was an error from stale BSData points). NO Lancer's Sigil. All points MFM-verified (1,970/2000 from data/mfm/imperial-knights.json).</t>
         </is>
       </c>
     </row>
@@ -1665,57 +1647,39 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Blessed Plate  [TAKEN]</t>
+          <t>Archeotech Autoloaders  [TAKEN — Castellan #1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the key Volcano platform. The 2-Armiger build fits ~one enhancement; this is it.</t>
+          <t>(25) Re-roll the number of Attacks (shots) of a weapon — huge on the Volcano lance (D3 shots) and plasma decimator (D6+3), turning low shot-rolls into full salvoes. The shooting-dominant enhancement.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>Bearer of the Judicant's Helm  [bench]</t>
+          <t>Blessed Plate  [TAKEN — Castellan #2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>a Knight Castellan</t>
+          <t>Knight Castellan</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>(25) [Ignores Cover] on a Castellan — stacks with Dominus +1-hit-in-terrain. Offensive alternative to Blessed Plate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Sanctuary  [bench]</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>a Knight Castellan</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>(20) 5++ invuln vs MELEE on one Castellan — patches the no-melee-invuln weakness (newly relevant: 11E has NO Rotate Ion Shields and Questoris have no melee save). Consider vs a melee-heavy field.</t>
+          <t>(30) Castellan -&gt; T13: pushes S12-13 anti-tank (rail / ferrumite / lascannon / Caladius / thermal) from wounding on 4+ to 5+ — survivability for the second Volcano platform.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C14:E14"/>
+  <mergeCells count="5">
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
@@ -1970,7 +1934,7 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Counter-charge the thunder-hammer brick; 4++ Lancer trades where a Castellan dies. (Not in the n=75 sample.)</t>
+          <t>Counter-charge the thunder-hammer brick; 4++ Lancer trades where a Castellan dies. (Not in the n=70 sample.)</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2627,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Knight Castellan (400)</t>
+          <t>Knight Castellan (425 / 450 escalating)</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">

--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DECISION" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta (n=75)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta (n=70)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List A" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List B" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matchups A vs B" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified Profiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sim Verification" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified Profiles" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2592,6 +2593,426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>DATA-DRIVEN SIM — A vs B (my Knights' output computed from data/bsdata via wh.mathhammer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>800 games/(list x archetype). tools/mc_db_sim.py. akR/akM = enemy anti-Knight EV/turn (ranged/melee, DB where present else verified floor); rmv = my EV onto their priority target/turn. Confirms: A wins SHOOTING metas, B wins MELEE metas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>prev</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>akR</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>akM</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>A rmv</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>B rmv</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>A win%</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>B win%</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Better list</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Emperor's Children (Defiler+swarm)</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Orks (Green Tide horde)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>AdMech (Rad-Zone gunline)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>T'au (Retaliation alpha)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Necrons (Awakened C'tan)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Custodes (elite melee)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Blood Angels (jump alpha)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Dark Angels (Deathwing bricks)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Drukhari (Skysplinter)</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Astra Militarum (superheavy)</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -635,7 +635,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>PREVALENCE-WEIGHTED TALLY (n=75 top lists)</t>
+          <t>PREVALENCE-WEIGHTED TALLY (n=70 top lists)</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>WINNERS' META — top-finishing lists, ~14 late-July-2026 GTs (n=75)</t>
+          <t>WINNERS' META — top-finishing lists, ~14 late-July-2026 GTs (n=70)</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Backfield 48" autocannon platform + OC6 screen.</t>
+          <t>Backfield 48" autocannon platform — BOND TO THE CRUSADER (Crusader's Duty Bondsman = +1 to hit -&gt; BS2+, 8 shots): consistent anti-infantry/light removal that fills the list's anti-scorer gap. Survivable OC6 home/backfield anchor (you're out-OC'd by most of the field) + Suppression Protocols (-1 to hit its target). Chosen over a Warglaive: the list's anti-tank is already over-solved (2x Volcano + thermal + shieldbreaker + Lancer), so add ranged volume + a body that survives to score, not a fragile forward melee piece that duplicates the Lancer.</t>
         </is>
       </c>
     </row>

--- a/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
+++ b/docs/Reports & Plans/LSO-Knights-List-Decision.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED profiles: Volcano lance 72" D3 shots S18 AP-5 D6+8 [Blast] = avg ~2 shots x ~11.5 = ~23 dmg into one target (one-shots a Hammerhead/Land Raider/Shadowsword/Kataphron brick/Ironstrider/Defiler and splits over) + plasma decimator 48" D6+3 shots S9 AP-4 D3 supercharge (~6.5 shots — shreds Terminators/elites, AP-4) + shieldbreaker S12 AP-6 D6+1 [Anti-Titanic 4+, Dev] character sniper. NET: ERASES ~1-2 extra priority targets PER TURN at range (bigger than first modelled — Volcano is D3, not 1). Wins the SHOOTING matchups.</t>
+          <t>VERIFIED profiles: Volcano lance 72" D3 shots S18 AP-5 D6+8 [Blast] = avg ~2 shots x ~11.5 = ~23 dmg into one target (one-shots a Hammerhead/Land Raider/Shadowsword/Kataphron brick/Ironstrider/Defiler and splits over) + plasma decimator 48" D6+3 shots S9 AP-4 D3 supercharge (~6.5 shots — shreds Terminators/elites, AP-4) + shieldbreaker S12 AP-6 D6+1 [Anti-Titanic 4+, Dev] — a TITANIC sniper (enemy Knights/superheavies), not an infantry-character sniper. NET: ERASES ~1-2 extra priority targets PER TURN at range (bigger than first modelled — Volcano is D3, not 1). Wins the SHOOTING matchups.</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>#1-tie. Lord Exultant+Infractors, Daemonettes/Tormentors, Flawless Blades, Maulerfiends + Defiler pair (ectoplasma S14 AP-3). Kill Defilers at range OR counter-charge the swarm.</t>
+          <t>#1-tie. Lord Exultant+Infractors, Daemonettes/Tormentors, Flawless Blades, Maulerfiends + Defiler pair (ectoplasma S12 AP-3). Kill Defilers at range OR counter-charge the swarm.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>The one blade: 4++ FULL invuln vs ALL, M14 W28. Counter-charge + assassinate buff-characters + Shock-Charge free Tank Shock on the charge.</t>
+          <t>The one blade: 4++ FULL invuln vs ALL, M14 W28. Counter-charge + kill characters (standalone monsters/Titanic DIRECTLY; ATTACHED buff-characters via EPIC CHALLENGE — 1CP core strat granting its melee [PRECISION]) + Shock-Charge free Tank Shock.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Character/tank sniper.</t>
+          <t>Anti-TITANIC (enemy Knights/superheavies) + tank sniper — NOT an infantry-character sniper (no Precision).</t>
         </is>
       </c>
     </row>
